--- a/tables/indicadores_percentis_renda_extendido.xlsx
+++ b/tables/indicadores_percentis_renda_extendido.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -506,6 +506,40 @@
       </c>
       <c r="J4">
         <v>265.2936220698696</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Nova c/ Aliq. Crescente</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>688.562633994668</v>
+      </c>
+      <c r="C5">
+        <v>1728.62326526626</v>
+      </c>
+      <c r="D5">
+        <v>34853.059284889</v>
+      </c>
+      <c r="E5">
+        <v>1040.060631271592</v>
+      </c>
+      <c r="F5">
+        <v>33124.43601962274</v>
+      </c>
+      <c r="G5">
+        <v>2.51048078987052</v>
+      </c>
+      <c r="H5">
+        <v>20.16232222786877</v>
+      </c>
+      <c r="I5">
+        <v>440922.022439792</v>
+      </c>
+      <c r="J5">
+        <v>255.0712068380479</v>
       </c>
     </row>
   </sheetData>
